--- a/etf_holdings/2026-09-29_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:26</t>
+          <t>2026-09-29 01:01:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:26</t>
+          <t>2026-09-29 01:01:27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:26</t>
+          <t>2026-09-29 01:01:27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:26</t>
+          <t>2026-09-29 01:01:27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:26</t>
+          <t>2026-09-29 01:01:27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:26</t>
+          <t>2026-09-29 01:01:27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:26</t>
+          <t>2026-09-29 01:01:27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:26</t>
+          <t>2026-09-29 01:01:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:26</t>
+          <t>2026-09-29 01:01:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:26</t>
+          <t>2026-09-29 01:01:27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:26</t>
+          <t>2026-09-29 01:01:27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:26</t>
+          <t>2026-09-29 01:01:27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:26</t>
+          <t>2026-09-29 01:01:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:26</t>
+          <t>2026-09-29 01:01:27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:26</t>
+          <t>2026-09-29 01:01:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:28</t>
+          <t>2026-09-29 01:01:28</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:28</t>
+          <t>2026-09-29 01:01:28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:28</t>
+          <t>2026-09-29 01:01:28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:28</t>
+          <t>2026-09-29 01:01:28</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:28</t>
+          <t>2026-09-29 01:01:28</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:28</t>
+          <t>2026-09-29 01:01:28</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:28</t>
+          <t>2026-09-29 01:01:28</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:28</t>
+          <t>2026-09-29 01:01:28</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:28</t>
+          <t>2026-09-29 01:01:28</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:28</t>
+          <t>2026-09-29 01:01:28</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:28</t>
+          <t>2026-09-29 01:01:28</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:28</t>
+          <t>2026-09-29 01:01:28</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:28</t>
+          <t>2026-09-29 01:01:28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:28</t>
+          <t>2026-09-29 01:01:28</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:28</t>
+          <t>2026-09-29 01:01:28</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:29</t>
+          <t>2026-09-29 01:01:29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:29</t>
+          <t>2026-09-29 01:01:29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:29</t>
+          <t>2026-09-29 01:01:29</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:29</t>
+          <t>2026-09-29 01:01:29</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:29</t>
+          <t>2026-09-29 01:01:29</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:29</t>
+          <t>2026-09-29 01:01:29</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:29</t>
+          <t>2026-09-29 01:01:29</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:29</t>
+          <t>2026-09-29 01:01:29</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:29</t>
+          <t>2026-09-29 01:01:29</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:29</t>
+          <t>2026-09-29 01:01:29</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:29</t>
+          <t>2026-09-29 01:01:29</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:29</t>
+          <t>2026-09-29 01:01:29</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">

--- a/etf_holdings/2026-09-29_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">

--- a/etf_holdings/2026-09-29_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:18</t>
+          <t>2026-09-29 22:55:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+2.45%3555</t>
+          <t>-4.36%3400</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>-4.36%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3555</v>
+        <v>3400</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.24%1,001,000</t>
+          <t>8.45%1,001,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.24%</t>
+          <t>8.45%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:18</t>
+          <t>2026-09-29 22:55:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+2.16%1185</t>
+          <t>-1.69%1165</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>-1.69%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1185</v>
+        <v>1165</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.83%2,482,000</t>
+          <t>6.98%2,482,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.83%</t>
+          <t>6.98%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:18</t>
+          <t>2026-09-29 22:55:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,12 +631,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1%2475</t>
+          <t>0%2475</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.62%1,116,000</t>
+          <t>6.56%1,116,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.62%</t>
+          <t>6.56%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:18</t>
+          <t>2026-09-29 22:55:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0%2340</t>
+          <t>+4.49%2445</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+4.49%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2340</v>
+        <v>2445</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:18</t>
+          <t>2026-09-29 22:55:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.32%12350</t>
+          <t>-1.9%12115</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>12350</v>
+        <v>12115</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.03%205,000</t>
+          <t>6.01%205,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.03%</t>
+          <t>6.01%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:18</t>
+          <t>2026-09-29 22:55:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.65%1530</t>
+          <t>+3.59%1585</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>+3.59%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1530</v>
+        <v>1585</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.96%1,630,000</t>
+          <t>5.92%1,630,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.96%</t>
+          <t>5.92%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:18</t>
+          <t>2026-09-29 22:55:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+0.6%5050</t>
+          <t>-2.57%4920</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>-2.57%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5050</v>
+        <v>4920</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.54%465,000</t>
+          <t>5.58%465,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.54%</t>
+          <t>5.58%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:18</t>
+          <t>2026-09-29 22:55:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.26%1895</t>
+          <t>-4.49%1810</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-4.49%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1895</v>
+        <v>1810</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.95%1,104,000</t>
+          <t>4.97%1,104,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.95%</t>
+          <t>4.97%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:18</t>
+          <t>2026-09-29 22:55:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.65%5415</t>
+          <t>-4.25%5185</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.65%</t>
+          <t>-4.25%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5415</v>
+        <v>5185</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.59%344,000</t>
+          <t>4.42%344,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.59%</t>
+          <t>4.42%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:18</t>
+          <t>2026-09-29 22:55:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+0.89%6245</t>
+          <t>-3.6%6020</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>6245</v>
+        <v>6020</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.30%293,000</t>
+          <t>4.35%293,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:18</t>
+          <t>2026-09-29 22:55:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.67%8525</t>
+          <t>-7.04%7925</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>-7.04%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8525</v>
+        <v>7925</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.26%164,000</t>
+          <t>3.32%164,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:18</t>
+          <t>2026-09-29 22:55:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1815富喬</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-3.33%116</t>
+          <t>+0.54%185.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.33%</t>
+          <t>+0.54%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>116</v>
+        <v>185.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.25%11,420,868</t>
+          <t>3.17%7,245,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>11420868</v>
+        <v>7245000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:18</t>
+          <t>2026-09-29 22:55:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>1815富喬</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+2.5%184.5</t>
+          <t>0%116</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+2.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>184.5</v>
+        <v>116</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.09%7,245,000</t>
+          <t>3.15%11,420,868</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>7245000</v>
+        <v>11420868</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:18</t>
+          <t>2026-09-29 22:55:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.42%480</t>
+          <t>0%480</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.04%2,682,000</t>
+          <t>3.06%2,682,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.06%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:18</t>
+          <t>2026-09-29 22:55:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>6584南俊國際</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+4.62%238</t>
+          <t>-0.18%543</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+4.62%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>238</v>
+        <v>543</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.94%5,445,000</t>
+          <t>2.86%2,213,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.86%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>5445000</v>
+        <v>2213000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:19</t>
+          <t>2026-09-29 22:55:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,25 +1419,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6584南俊國際</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+0.37%544</t>
+          <t>+2.42%1270</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+2.42%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>544</v>
+        <v>1270</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.85%2,213,000</t>
+          <t>2.85%968,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1446,11 +1446,11 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2213000</v>
+        <v>968000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:19</t>
+          <t>2026-09-29 22:55:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+2.48%1240</t>
+          <t>-7.1%4910</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+2.48%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1240</v>
+        <v>4910</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.78%968,000</t>
+          <t>2.25%179,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.25%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>968000</v>
+        <v>179000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:19</t>
+          <t>2026-09-29 22:55:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+0.36%554</t>
+          <t>-1.99%543</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-1.99%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.23%1,700,000</t>
+          <t>2.24%1,700,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.24%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:19</t>
+          <t>2026-09-29 22:55:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+1.93%5285</t>
+          <t>-0.71%2100</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5285</v>
+        <v>2100</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.20%179,000</t>
+          <t>2.16%429,675</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.16%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>179000</v>
+        <v>429675</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:19</t>
+          <t>2026-09-29 22:55:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+0.48%2115</t>
+          <t>+3.78%247</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2115</v>
+        <v>247</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.15%429,675</t>
+          <t>2.06%3,645,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.06%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>429675</v>
+        <v>3645000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:19</t>
+          <t>2026-09-29 22:55:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+6.18%962</t>
+          <t>-0.73%955</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+6.18%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.81%844,013</t>
+          <t>1.93%844,013</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:19</t>
+          <t>2026-09-29 22:55:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.53%475.5</t>
+          <t>+4.84%498.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+4.84%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>475.5</v>
+        <v>498.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.12%1,000,000</t>
+          <t>1.13%1,000,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:19</t>
+          <t>2026-09-29 22:55:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+0.53%1910</t>
+          <t>-3.93%1835</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>-3.93%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1910</v>
+        <v>1835</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.90%200,000</t>
+          <t>0.91%200,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:19</t>
+          <t>2026-09-29 22:55:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-2.42%5850</t>
+          <t>-2.99%5675</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>5850</v>
+        <v>5675</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.73%51,000</t>
+          <t>0.71%51,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:19</t>
+          <t>2026-09-29 22:55:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-2.19%19835</t>
+          <t>-0.36%6895</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>19835</v>
+        <v>6895</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.53%11,000</t>
+          <t>0.54%33,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>11000</v>
+        <v>33000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:19</t>
+          <t>2026-09-29 22:55:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+7.96%6920</t>
+          <t>+4.2%620</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+7.96%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>6920</v>
+        <v>620</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.50%33,000</t>
+          <t>0.53%373,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>33000</v>
+        <v>373000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:19</t>
+          <t>2026-09-29 22:55:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+4.67%112</t>
+          <t>-6.7%104.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+4.67%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>112</v>
+        <v>104.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.50%1,957,000</t>
+          <t>0.52%1,957,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:19</t>
+          <t>2026-09-29 22:55:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+9.98%595</t>
+          <t>-2.22%19395</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+9.98%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>595</v>
+        <v>19395</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.48%373,000</t>
+          <t>0.52%11,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>373000</v>
+        <v>11000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:19</t>
+          <t>2026-09-29 22:55:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+5.47%810</t>
+          <t>-1.73%796</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+5.47%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>810</v>
+        <v>796</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.48%261,000</t>
+          <t>0.50%261,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:19</t>
+          <t>2026-09-29 22:55:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+2.8%1285</t>
+          <t>-5.06%1220</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+2.8%</t>
+          <t>-5.06%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1285</v>
+        <v>1220</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.46%155,000</t>
+          <t>0.47%155,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:20</t>
+          <t>2026-09-29 22:55:52</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,25 +2334,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2357華碩</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.52%953</t>
+          <t>-2.09%281</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>953</v>
+        <v>281</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.45%196,000</t>
+          <t>0.45%659,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2361,11 +2361,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>196000</v>
+        <v>659000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:20</t>
+          <t>2026-09-29 22:55:52</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>6139亞翔</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.23%287</t>
+          <t>-2.79%732</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-2.79%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>287</v>
+        <v>732</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.44%659,000</t>
+          <t>0.45%250,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>659000</v>
+        <v>250000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:20</t>
+          <t>2026-09-29 22:55:52</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,25 +2456,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>2357華碩</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.96%361.5</t>
+          <t>+1.05%963</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>361.5</v>
+        <v>963</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.44%508,000</t>
+          <t>0.44%196,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2483,11 +2483,11 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>508000</v>
+        <v>196000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:20</t>
+          <t>2026-09-29 22:55:52</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,25 +2517,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6139亞翔</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+2.31%753</t>
+          <t>+0.14%362</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>753</v>
+        <v>362</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.44%250,000</t>
+          <t>0.44%508,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2544,11 +2544,11 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>250000</v>
+        <v>508000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:20</t>
+          <t>2026-09-29 22:55:52</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,34 +2578,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-1.29%2295</t>
+          <t>-1.72%687</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2295</v>
+        <v>687</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.42%76,000</t>
+          <t>0.41%250,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>76000</v>
+        <v>250000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:20</t>
+          <t>2026-09-29 22:55:52</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.87%699</t>
+          <t>-4.79%2185</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>-4.79%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>699</v>
+        <v>2185</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.41%250,000</t>
+          <t>0.41%76,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,11 +2666,11 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>250000</v>
+        <v>76000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:20</t>
+          <t>2026-09-29 22:55:52</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.75%2700</t>
+          <t>-1.85%2650</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.75%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2700</v>
+        <v>2650</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:20</t>
+          <t>2026-09-29 22:55:52</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+2.4%1495</t>
+          <t>-0.67%1485</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1495</v>
+        <v>1485</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.39%113,000</t>
+          <t>0.40%113,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:20</t>
+          <t>2026-09-29 22:55:52</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.83%1195</t>
+          <t>+9.62%1310</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.83%</t>
+          <t>+9.62%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1195</v>
+        <v>1310</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:20</t>
+          <t>2026-09-29 22:55:52</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0%1305</t>
+          <t>-1.92%1280</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.92%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1305</v>
+        <v>1280</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:20</t>
+          <t>2026-09-29 22:55:52</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-1.45%170.5</t>
+          <t>+4.69%178.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>+4.69%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>170.5</v>
+        <v>178.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.26%629,000</t>
+          <t>0.25%629,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:20</t>
+          <t>2026-09-29 22:55:52</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+1.9%2410</t>
+          <t>+2.7%2475</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+1.9%</t>
+          <t>+2.7%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2410</v>
+        <v>2475</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-29_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:30</t>
+          <t>2026-09-29 23:06:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:30</t>
+          <t>2026-09-29 23:06:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:30</t>
+          <t>2026-09-29 23:06:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:30</t>
+          <t>2026-09-29 23:06:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:30</t>
+          <t>2026-09-29 23:06:49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:30</t>
+          <t>2026-09-29 23:06:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:30</t>
+          <t>2026-09-29 23:06:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:30</t>
+          <t>2026-09-29 23:06:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:30</t>
+          <t>2026-09-29 23:06:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:30</t>
+          <t>2026-09-29 23:06:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:30</t>
+          <t>2026-09-29 23:06:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:30</t>
+          <t>2026-09-29 23:06:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:30</t>
+          <t>2026-09-29 23:06:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:30</t>
+          <t>2026-09-29 23:06:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:30</t>
+          <t>2026-09-29 23:06:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:41</t>
+          <t>2026-09-29 23:06:50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:41</t>
+          <t>2026-09-29 23:06:50</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:41</t>
+          <t>2026-09-29 23:06:50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:41</t>
+          <t>2026-09-29 23:06:50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:41</t>
+          <t>2026-09-29 23:06:50</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:41</t>
+          <t>2026-09-29 23:06:50</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:41</t>
+          <t>2026-09-29 23:06:50</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:41</t>
+          <t>2026-09-29 23:06:50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:41</t>
+          <t>2026-09-29 23:06:50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:41</t>
+          <t>2026-09-29 23:06:50</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:41</t>
+          <t>2026-09-29 23:06:50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:41</t>
+          <t>2026-09-29 23:06:50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:41</t>
+          <t>2026-09-29 23:06:50</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:41</t>
+          <t>2026-09-29 23:06:50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:41</t>
+          <t>2026-09-29 23:06:50</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:52</t>
+          <t>2026-09-29 23:06:51</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:52</t>
+          <t>2026-09-29 23:06:51</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:52</t>
+          <t>2026-09-29 23:06:51</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:52</t>
+          <t>2026-09-29 23:06:51</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:52</t>
+          <t>2026-09-29 23:06:51</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:52</t>
+          <t>2026-09-29 23:06:51</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:52</t>
+          <t>2026-09-29 23:06:51</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:52</t>
+          <t>2026-09-29 23:06:51</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:52</t>
+          <t>2026-09-29 23:06:51</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:52</t>
+          <t>2026-09-29 23:06:51</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:52</t>
+          <t>2026-09-29 23:06:51</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:52</t>
+          <t>2026-09-29 23:06:51</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">

--- a/etf_holdings/2026-09-29_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:49</t>
+          <t>2026-09-29 23:51:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:49</t>
+          <t>2026-09-29 23:51:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:49</t>
+          <t>2026-09-29 23:51:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:49</t>
+          <t>2026-09-29 23:51:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:49</t>
+          <t>2026-09-29 23:51:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:49</t>
+          <t>2026-09-29 23:51:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:49</t>
+          <t>2026-09-29 23:51:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:49</t>
+          <t>2026-09-29 23:51:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:49</t>
+          <t>2026-09-29 23:51:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:49</t>
+          <t>2026-09-29 23:51:56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:49</t>
+          <t>2026-09-29 23:51:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:49</t>
+          <t>2026-09-29 23:51:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:49</t>
+          <t>2026-09-29 23:51:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:49</t>
+          <t>2026-09-29 23:51:56</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:49</t>
+          <t>2026-09-29 23:51:56</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:50</t>
+          <t>2026-09-29 23:51:57</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:50</t>
+          <t>2026-09-29 23:51:57</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:50</t>
+          <t>2026-09-29 23:51:57</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:50</t>
+          <t>2026-09-29 23:51:57</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:50</t>
+          <t>2026-09-29 23:51:57</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:50</t>
+          <t>2026-09-29 23:51:57</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:50</t>
+          <t>2026-09-29 23:51:57</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:50</t>
+          <t>2026-09-29 23:51:57</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:50</t>
+          <t>2026-09-29 23:51:57</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:50</t>
+          <t>2026-09-29 23:51:57</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:50</t>
+          <t>2026-09-29 23:51:57</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:50</t>
+          <t>2026-09-29 23:51:57</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:50</t>
+          <t>2026-09-29 23:51:57</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:50</t>
+          <t>2026-09-29 23:51:57</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:50</t>
+          <t>2026-09-29 23:51:57</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:51</t>
+          <t>2026-09-29 23:51:59</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:51</t>
+          <t>2026-09-29 23:51:59</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:51</t>
+          <t>2026-09-29 23:51:59</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:51</t>
+          <t>2026-09-29 23:51:59</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:51</t>
+          <t>2026-09-29 23:51:59</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:51</t>
+          <t>2026-09-29 23:51:59</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:51</t>
+          <t>2026-09-29 23:51:59</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:51</t>
+          <t>2026-09-29 23:51:59</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:51</t>
+          <t>2026-09-29 23:51:59</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:51</t>
+          <t>2026-09-29 23:51:59</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:51</t>
+          <t>2026-09-29 23:51:59</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:51</t>
+          <t>2026-09-29 23:51:59</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
